--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129566448</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57721</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Annehill, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567599</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626240</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129566448</v>
       </c>
       <c r="B3" t="n">
-        <v>57721</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129566448</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129566448</v>
       </c>
       <c r="B3" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129566448</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102481546</v>
+        <v>56307</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,27 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Annehill, Ramnäs sn, Vstm</t>
+          <t>Hopslagarvägen, Ramnäs, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567598.8468116235</v>
+        <v>567370</v>
       </c>
       <c r="R2" t="n">
-        <v>6626239.801596883</v>
+        <v>6626343</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rapportör: Olle o Gudrun Lager</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129566448</v>
+        <v>102481546</v>
       </c>
       <c r="B3" t="n">
-        <v>57731</v>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100053</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>trafikdödad</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -876,22 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +897,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129566448</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Annehill, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567599</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626240</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40403-2025 artfynd.xlsx
+++ b/artfynd/A 40403-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102481546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,8 +1031,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129566448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>